--- a/ruoyi-modules/ruoyi-vehicle/src/main/resources/assets/COC模版.xlsx
+++ b/ruoyi-modules/ruoyi-vehicle/src/main/resources/assets/COC模版.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12300"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -566,8 +566,8 @@
     <t>56. Vehicle certified in accordance with UN Regulation No 156:</t>
   </si>
   <si>
-    <t>黄色背景数据为示例数据，Vehicle Type中数据于0.4. Vehicle category:中数据相同，导入时请从第三行开始录入数据。
-Data with a yellow background is example data. The data in Vehicle Type is 0.4. The data in Vehicle category are the same. When importing, please start entering data from the third row.</t>
+    <t>黄色背景数据为示例数据，Vehicle Type中数据于0.4. Vehicle category:中数据相同，导入时请从第五行开始录入数据。
+Data with a yellow background is example data. The data in Vehicle Type is 0.4. The data in Vehicle category are the same. When importing, please start entering data from the fifth row.</t>
   </si>
   <si>
     <t>COC0001</t>

--- a/ruoyi-modules/ruoyi-vehicle/src/main/resources/assets/COC模版.xlsx
+++ b/ruoyi-modules/ruoyi-vehicle/src/main/resources/assets/COC模版.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="424">
   <si>
     <t>COC Template No.</t>
   </si>
@@ -35,12 +35,42 @@
     <t>WVTA-COC No.</t>
   </si>
   <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>tvv</t>
+  </si>
+  <si>
     <t>Model No.</t>
   </si>
   <si>
+    <t>Vehicle category</t>
+  </si>
+  <si>
+    <t>Effective date</t>
+  </si>
+  <si>
+    <t>Overdue date</t>
+  </si>
+  <si>
+    <t>Remark</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Validate result</t>
+  </si>
+  <si>
+    <t>First  vehicle validate</t>
+  </si>
+  <si>
     <t>Signatory.</t>
   </si>
   <si>
+    <t>Signer Position.</t>
+  </si>
+  <si>
     <t>0.1. Make (Trade name of manufacturer):</t>
   </si>
   <si>
@@ -83,9 +113,6 @@
     <t>0.2.3.8 OBD family's identifier</t>
   </si>
   <si>
-    <t>Vehicle Type</t>
-  </si>
-  <si>
     <t>0.4. Vehicle category:</t>
   </si>
   <si>
@@ -332,13 +359,13 @@
     <t>42.3. Number of wheelchair user accessible position:</t>
   </si>
   <si>
-    <t>46. Sound level</t>
-  </si>
-  <si>
-    <t>46. Stationary:</t>
-  </si>
-  <si>
-    <t>46. Drive-by:</t>
+    <t>46.a Sound level</t>
+  </si>
+  <si>
+    <t>46.b Stationary:</t>
+  </si>
+  <si>
+    <t>46.c Drive-by:</t>
   </si>
   <si>
     <t>47. Exhaust emission level:</t>
@@ -437,7 +464,52 @@
     <t>49. CO2 emissions/fuel consumption/electric energy consumption:</t>
   </si>
   <si>
-    <t xml:space="preserve">49. 1. all power train except pure electric vehicles(if applicable): </t>
+    <t xml:space="preserve">49. 1.a all power train except pure electric vehicles(if applicable): </t>
+  </si>
+  <si>
+    <t>49. 1.b Low CO2 emissions</t>
+  </si>
+  <si>
+    <t>49. 1.c Low Fuel consumption</t>
+  </si>
+  <si>
+    <t>49. 1.d Low Electric Consumption (ECAC)</t>
+  </si>
+  <si>
+    <t>49. 1.e Medium CO2 emissions</t>
+  </si>
+  <si>
+    <t>49. 1.f Medium Fuel consumption</t>
+  </si>
+  <si>
+    <t>49. 1.g Medium Electric Consumption (ECAC)</t>
+  </si>
+  <si>
+    <t>49. 1.h High CO2 emissions</t>
+  </si>
+  <si>
+    <t>49. 1.i High Fuel consumption</t>
+  </si>
+  <si>
+    <t>49. 1.j High Electric Consumption (ECAC)</t>
+  </si>
+  <si>
+    <t>49. 1.k Extra High CO2 emissions</t>
+  </si>
+  <si>
+    <t>49. 1.l Extra High Fuel consumption</t>
+  </si>
+  <si>
+    <t>49. 1.m Extra High Electric Consumption (ECAC)</t>
+  </si>
+  <si>
+    <t>49. 1.n Combined CO2 emissions</t>
+  </si>
+  <si>
+    <t>49. 1.o Combined Fuel consumption</t>
+  </si>
+  <si>
+    <t>49. 1.p Combined Electric Consumption (ECAC)</t>
   </si>
   <si>
     <t>49. 2.a Electric range of pure electric vehicles (if applicable):</t>
@@ -566,8 +638,8 @@
     <t>56. Vehicle certified in accordance with UN Regulation No 156:</t>
   </si>
   <si>
-    <t>黄色背景数据为示例数据，Vehicle Type中数据于0.4. Vehicle category:中数据相同，导入时请从第五行开始录入数据。
-Data with a yellow background is example data. The data in Vehicle Type is 0.4. The data in Vehicle category are the same. When importing, please start entering data from the fifth row.</t>
+    <t>黄色背景数据为示例数据，Vehicle Type中数据于0.4. Vehicle category:中数据相同，导入时请从第五行开始录入数据。红色表头为必填数据项。
+Data with a yellow background is example data. The data in Vehicle Type is 0.4. The data in Vehicle category are the same. When importing, please start entering data from the fifth row.Red headers indicate required data fields.</t>
   </si>
   <si>
     <t>COC0001</t>
@@ -576,12 +648,39 @@
     <t>11329-07&amp;177&amp;99V&amp;COC001-EB</t>
   </si>
   <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>T31FPL4BL72E447T</t>
+  </si>
+  <si>
     <t>SQR6470T18TBE</t>
   </si>
   <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>2026/5/1 9:01:05</t>
+  </si>
+  <si>
+    <t>2026/7/1 9:01:05</t>
+  </si>
+  <si>
+    <t>备注1</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
     <t>Zhai Ying</t>
   </si>
   <si>
+    <t>Quality director</t>
+  </si>
+  <si>
     <t>CHERY</t>
   </si>
   <si>
@@ -616,9 +715,6 @@
   </si>
   <si>
     <t>OB-PHEMG1US0281_02-LNN</t>
-  </si>
-  <si>
-    <t>M1</t>
   </si>
   <si>
     <t>CHERY AUTOMOBILE CO., LTD.No.8 Changchun Road, Economic and Technological Development Zone 241006, Wuhu, ANHUI (CHINA)</t>
@@ -698,8 +794,7 @@
 Wuhu ACTECO Power Systems Co., </t>
   </si>
   <si>
-    <t>Front: YS190XY101
-Rear: TZ220XSG05</t>
+    <t>SQRH4J15</t>
   </si>
   <si>
     <t>E4,EE</t>
@@ -764,6 +859,9 @@
     <t>1604</t>
   </si>
   <si>
+    <t>235/50R19 103V 19x7J ET47 6.28N/kN C1</t>
+  </si>
+  <si>
     <t>235/50 R19 103V 19x7J ET47 6.28N/kN C1</t>
   </si>
   <si>
@@ -785,7 +883,7 @@
     <t>77dB(A) at 3750 min-1</t>
   </si>
   <si>
-    <t xml:space="preserve"> 67dB(A)</t>
+    <t>67dB(A)</t>
   </si>
   <si>
     <t>Euro 6e (EB)</t>
@@ -833,6 +931,36 @@
     <t>PN: 8.04E+11 #/km</t>
   </si>
   <si>
+    <t>195 g/km</t>
+  </si>
+  <si>
+    <t>8.6L /100km</t>
+  </si>
+  <si>
+    <t>153 g/km</t>
+  </si>
+  <si>
+    <t>6.7L /100km</t>
+  </si>
+  <si>
+    <t>139 g/km</t>
+  </si>
+  <si>
+    <t>6.1L /100km</t>
+  </si>
+  <si>
+    <t>167 g/km</t>
+  </si>
+  <si>
+    <t>7.4L /100km</t>
+  </si>
+  <si>
+    <t>159 g/km</t>
+  </si>
+  <si>
+    <t>7.0L /100km</t>
+  </si>
+  <si>
     <t>142 g/km</t>
   </si>
   <si>
@@ -896,6 +1024,9 @@
     <t>181 Wh/km</t>
   </si>
   <si>
+    <t>92km</t>
+  </si>
+  <si>
     <t>145km</t>
   </si>
   <si>
@@ -911,16 +1042,22 @@
     <t>TPMS/ELKS/AEBS/ESS/AIF/ISA/DDAW/ADDW/EDR/~~DAM/ADS@@/eCall</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>COC0002</t>
   </si>
   <si>
     <t>11785-02&amp;120&amp;99H&amp;COC002-EB</t>
   </si>
   <si>
+    <t>T341DHL4BL54E25DA</t>
+  </si>
+  <si>
     <t>T19C HEV</t>
+  </si>
+  <si>
+    <t>备注2</t>
+  </si>
+  <si>
+    <t>Reject</t>
   </si>
   <si>
     <t>OMODA</t>
@@ -1003,10 +1140,7 @@
 heifei JEE Power Systems CO.,Ltd(Rear)</t>
   </si>
   <si>
-    <t>Engine:SQRH4J15
-EM1&amp;EM2:KPTZ270YMXA0
-KPTZ180YMXA0
-Rear:TZ190XYCY1</t>
+    <t>KPTZ220YMDA0</t>
   </si>
   <si>
     <t>Positive ignition</t>
@@ -1075,7 +1209,7 @@
     <t>65dB(A) at 3750 min-1</t>
   </si>
   <si>
-    <t xml:space="preserve"> 68dB(A)</t>
+    <t>68dB(A)</t>
   </si>
   <si>
     <t>1707kg</t>
@@ -1111,6 +1245,42 @@
     <t>0.00</t>
   </si>
   <si>
+    <t>185 g/km</t>
+  </si>
+  <si>
+    <t>8.2L /100km</t>
+  </si>
+  <si>
+    <t>100 l/100km</t>
+  </si>
+  <si>
+    <t>123 g/km</t>
+  </si>
+  <si>
+    <t>88 l/km</t>
+  </si>
+  <si>
+    <t>128 g/km</t>
+  </si>
+  <si>
+    <t>5.6L /100km</t>
+  </si>
+  <si>
+    <t>72 l/kg</t>
+  </si>
+  <si>
+    <t>5.1L /100km</t>
+  </si>
+  <si>
+    <t>97.3 l/km</t>
+  </si>
+  <si>
+    <t>114 g/km</t>
+  </si>
+  <si>
+    <t>66 l/km</t>
+  </si>
+  <si>
     <t>120 g/km</t>
   </si>
   <si>
@@ -1163,6 +1333,9 @@
   </si>
   <si>
     <t>121 Wh/km</t>
+  </si>
+  <si>
+    <t>18km</t>
   </si>
   <si>
     <t>112km</t>
@@ -1375,7 +1548,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1385,6 +1558,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1764,7 +1943,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1788,16 +1967,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1806,89 +1985,89 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1898,6 +2077,9 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1907,10 +2089,10 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2450,21 +2632,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:FW4"/>
+  <dimension ref="A1:GU4"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3"/>
   <cols>
-    <col min="7" max="7" width="26" customWidth="1"/>
-    <col min="9" max="9" width="96.2222222222222" customWidth="1"/>
-    <col min="13" max="13" width="28.7777777777778" customWidth="1"/>
-    <col min="15" max="15" width="20.7777777777778" customWidth="1"/>
-    <col min="26" max="26" width="17.8888888888889" customWidth="1"/>
-    <col min="80" max="80" width="32.7777777777778" customWidth="1"/>
-    <col min="95" max="95" width="47.5555555555556" customWidth="1"/>
-    <col min="97" max="97" width="37.7777777777778" customWidth="1"/>
-    <col min="99" max="99" width="103.222222222222" customWidth="1"/>
+    <col min="7" max="7" width="9.66666666666667" customWidth="1"/>
+    <col min="17" max="17" width="26" customWidth="1"/>
+    <col min="19" max="19" width="96.2222222222222" customWidth="1"/>
+    <col min="23" max="23" width="28.7777777777778" customWidth="1"/>
+    <col min="25" max="25" width="20.7777777777778" customWidth="1"/>
+    <col min="35" max="35" width="17.8888888888889" customWidth="1"/>
+    <col min="89" max="89" width="32.7777777777778" customWidth="1"/>
+    <col min="104" max="104" width="47.5555555555556" customWidth="1"/>
+    <col min="106" max="106" width="37.7777777777778" customWidth="1"/>
+    <col min="108" max="108" width="103.222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="144" customHeight="1" spans="1:179">
+    <row r="1" ht="144" customHeight="1" spans="1:203">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2477,7 +2660,7 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -2486,1697 +2669,1943 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="7" t="s">
         <v>19</v>
       </c>
       <c r="U1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="V1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AI1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AN1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AO1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AP1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AR1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AS1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AT1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AU1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AV1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AW1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AX1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AY1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BA1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BB1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BC1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BD1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BE1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BF1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BG1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BH1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="2" t="s">
+      <c r="BI1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="2" t="s">
+      <c r="BJ1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BK1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="2" t="s">
+      <c r="BL1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="2" t="s">
+      <c r="BM1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="2" t="s">
+      <c r="BN1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="2" t="s">
+      <c r="BO1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="2" t="s">
+      <c r="BP1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="2" t="s">
+      <c r="BQ1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="2" t="s">
+      <c r="BR1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BS1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="6" t="s">
+      <c r="BT1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" s="6" t="s">
+      <c r="BU1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" s="6" t="s">
+      <c r="BV1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" s="6" t="s">
+      <c r="BW1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="BX1" s="6" t="s">
+      <c r="BX1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="BY1" s="6" t="s">
+      <c r="BY1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="BZ1" s="6" t="s">
+      <c r="BZ1" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="CA1" s="6" t="s">
+      <c r="CA1" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="CB1" s="6" t="s">
+      <c r="CB1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="CC1" s="6" t="s">
+      <c r="CC1" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="6" t="s">
+      <c r="CD1" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="CE1" s="6" t="s">
+      <c r="CE1" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="CF1" s="6" t="s">
+      <c r="CF1" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="CG1" s="6" t="s">
+      <c r="CG1" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="CH1" s="6" t="s">
+      <c r="CH1" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="CI1" s="6" t="s">
+      <c r="CI1" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="CJ1" s="6" t="s">
+      <c r="CJ1" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="CK1" s="2" t="s">
+      <c r="CK1" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="CL1" s="2" t="s">
+      <c r="CL1" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="CM1" s="2" t="s">
+      <c r="CM1" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="CN1" s="2" t="s">
+      <c r="CN1" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="CO1" s="2" t="s">
+      <c r="CO1" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="CP1" s="2" t="s">
+      <c r="CP1" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="CQ1" s="2" t="s">
+      <c r="CQ1" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="CR1" s="2" t="s">
+      <c r="CR1" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="CS1" s="2" t="s">
+      <c r="CS1" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="CT1" s="2" t="s">
+      <c r="CT1" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="CU1" s="2" t="s">
+      <c r="CU1" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="CV1" s="2" t="s">
+      <c r="CV1" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="CW1" s="2" t="s">
+      <c r="CW1" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="CX1" s="2" t="s">
+      <c r="CX1" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="CY1" s="2" t="s">
+      <c r="CY1" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="CZ1" s="2" t="s">
+      <c r="CZ1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="DA1" s="2" t="s">
+      <c r="DA1" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="DB1" s="2" t="s">
+      <c r="DB1" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="DC1" s="2" t="s">
+      <c r="DC1" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="DD1" s="2" t="s">
+      <c r="DD1" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="DE1" s="2" t="s">
+      <c r="DE1" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="DF1" s="2" t="s">
+      <c r="DF1" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="DG1" s="2" t="s">
+      <c r="DG1" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="DH1" s="2" t="s">
+      <c r="DH1" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="DI1" s="2" t="s">
+      <c r="DI1" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="DJ1" s="2" t="s">
+      <c r="DJ1" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="DK1" s="2" t="s">
+      <c r="DK1" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="DL1" s="2" t="s">
+      <c r="DL1" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="DM1" s="2" t="s">
+      <c r="DM1" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="DN1" s="2" t="s">
+      <c r="DN1" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="DO1" s="2" t="s">
+      <c r="DO1" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="DP1" s="2" t="s">
+      <c r="DP1" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="DQ1" s="2" t="s">
+      <c r="DQ1" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="DR1" s="2" t="s">
+      <c r="DR1" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="DS1" s="2" t="s">
+      <c r="DS1" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="DT1" s="2" t="s">
+      <c r="DT1" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="DU1" s="2" t="s">
+      <c r="DU1" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="DV1" s="2" t="s">
+      <c r="DV1" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="DW1" s="2" t="s">
+      <c r="DW1" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="DX1" s="2" t="s">
+      <c r="DX1" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="DY1" s="2" t="s">
+      <c r="DY1" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="DZ1" s="2" t="s">
+      <c r="DZ1" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="EA1" s="2" t="s">
+      <c r="EA1" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="EB1" s="2" t="s">
+      <c r="EB1" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="EC1" s="2" t="s">
+      <c r="EC1" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="ED1" s="2" t="s">
+      <c r="ED1" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="EE1" s="6" t="s">
+      <c r="EE1" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="EF1" s="2" t="s">
+      <c r="EF1" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="EG1" s="2" t="s">
+      <c r="EG1" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="EH1" s="2" t="s">
+      <c r="EH1" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="EI1" s="2" t="s">
+      <c r="EI1" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="EJ1" s="2" t="s">
+      <c r="EJ1" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="EK1" s="2" t="s">
+      <c r="EK1" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="EL1" s="2" t="s">
+      <c r="EL1" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="EM1" s="2" t="s">
+      <c r="EM1" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="EN1" s="2" t="s">
+      <c r="EN1" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="EO1" s="2" t="s">
+      <c r="EO1" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="EP1" s="2" t="s">
+      <c r="EP1" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="EQ1" s="2" t="s">
+      <c r="EQ1" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="ER1" s="2" t="s">
+      <c r="ER1" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="ES1" s="2" t="s">
+      <c r="ES1" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="ET1" s="2" t="s">
+      <c r="ET1" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="EU1" s="2" t="s">
+      <c r="EU1" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="EV1" s="2" t="s">
+      <c r="EV1" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="EW1" s="2" t="s">
+      <c r="EW1" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="EX1" s="2" t="s">
+      <c r="EX1" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="EY1" s="2" t="s">
+      <c r="EY1" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="EZ1" s="2" t="s">
+      <c r="EZ1" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="FA1" s="2" t="s">
+      <c r="FA1" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="FB1" s="2" t="s">
+      <c r="FB1" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="FC1" s="2" t="s">
+      <c r="FC1" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="FD1" s="2" t="s">
+      <c r="FD1" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="FE1" s="2" t="s">
+      <c r="FE1" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="FF1" s="2" t="s">
+      <c r="FF1" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="FG1" s="2" t="s">
+      <c r="FG1" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="FH1" s="2" t="s">
+      <c r="FH1" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="FI1" s="2" t="s">
+      <c r="FI1" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="FJ1" s="2" t="s">
+      <c r="FJ1" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="FK1" s="2" t="s">
+      <c r="FK1" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="FL1" s="2" t="s">
+      <c r="FL1" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="FM1" s="2" t="s">
+      <c r="FM1" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="FN1" s="2" t="s">
+      <c r="FN1" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="FO1" s="2" t="s">
+      <c r="FO1" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="FP1" s="2" t="s">
+      <c r="FP1" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="FQ1" s="2" t="s">
+      <c r="FQ1" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="FR1" s="2" t="s">
+      <c r="FR1" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="FS1" s="2" t="s">
+      <c r="FS1" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="FT1" s="2" t="s">
+      <c r="FT1" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="FU1" s="2" t="s">
+      <c r="FU1" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="FV1" s="2" t="s">
+      <c r="FV1" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="FW1" s="2" t="s">
+      <c r="FW1" s="3" t="s">
         <v>178</v>
       </c>
+      <c r="FX1" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="FY1" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="FZ1" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="GA1" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="GB1" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="GC1" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="GD1" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="GE1" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="GF1" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="GG1" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="GH1" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="GI1" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="GJ1" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="GK1" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="GL1" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="GM1" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="GN1" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="GO1" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="GP1" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="GQ1" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="GR1" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="GS1" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="GT1" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="GU1" s="3" t="s">
+        <v>202</v>
+      </c>
     </row>
-    <row r="2" customFormat="1" ht="34" customHeight="1" spans="1:179">
-      <c r="A2" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
-      <c r="AF2" s="4"/>
-      <c r="AG2" s="4"/>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
-      <c r="AJ2" s="4"/>
-      <c r="AK2" s="4"/>
-      <c r="AL2" s="4"/>
-      <c r="AM2" s="4"/>
-      <c r="AN2" s="4"/>
-      <c r="AO2" s="4"/>
-      <c r="AP2" s="4"/>
-      <c r="AQ2" s="4"/>
-      <c r="AR2" s="4"/>
-      <c r="AS2" s="4"/>
-      <c r="AT2" s="4"/>
-      <c r="AU2" s="4"/>
-      <c r="AV2" s="4"/>
-      <c r="AW2" s="4"/>
-      <c r="AX2" s="4"/>
-      <c r="AY2" s="4"/>
-      <c r="AZ2" s="4"/>
-      <c r="BA2" s="4"/>
-      <c r="BB2" s="4"/>
-      <c r="BC2" s="4"/>
-      <c r="BD2" s="4"/>
-      <c r="BE2" s="4"/>
-      <c r="BF2" s="4"/>
-      <c r="BG2" s="4"/>
-      <c r="BH2" s="4"/>
-      <c r="BI2" s="4"/>
-      <c r="BJ2" s="4"/>
-      <c r="BK2" s="4"/>
-      <c r="BL2" s="4"/>
-      <c r="BM2" s="4"/>
-      <c r="BN2" s="4"/>
-      <c r="BO2" s="4"/>
-      <c r="BP2" s="4"/>
-      <c r="BQ2" s="4"/>
-      <c r="BR2" s="4"/>
-      <c r="BS2" s="4"/>
-      <c r="BT2" s="4"/>
-      <c r="BU2" s="4"/>
-      <c r="BV2" s="4"/>
-      <c r="BW2" s="4"/>
-      <c r="BX2" s="4"/>
-      <c r="BY2" s="4"/>
-      <c r="BZ2" s="4"/>
-      <c r="CA2" s="4"/>
-      <c r="CB2" s="4"/>
-      <c r="CC2" s="4"/>
-      <c r="CD2" s="4"/>
-      <c r="CE2" s="4"/>
-      <c r="CF2" s="4"/>
-      <c r="CG2" s="4"/>
-      <c r="CH2" s="4"/>
-      <c r="CI2" s="4"/>
-      <c r="CJ2" s="4"/>
-      <c r="CK2" s="4"/>
-      <c r="CL2" s="4"/>
-      <c r="CM2" s="4"/>
-      <c r="CN2" s="4"/>
-      <c r="CO2" s="4"/>
-      <c r="CP2" s="4"/>
-      <c r="CQ2" s="4"/>
-      <c r="CR2" s="4"/>
-      <c r="CS2" s="4"/>
-      <c r="CT2" s="4"/>
-      <c r="CU2" s="4"/>
-      <c r="CV2" s="4"/>
-      <c r="CW2" s="4"/>
-      <c r="CX2" s="4"/>
-      <c r="CY2" s="4"/>
-      <c r="CZ2" s="4"/>
-      <c r="DA2" s="4"/>
-      <c r="DB2" s="4"/>
-      <c r="DC2" s="4"/>
-      <c r="DD2" s="4"/>
-      <c r="DE2" s="4"/>
-      <c r="DF2" s="4"/>
-      <c r="DG2" s="4"/>
-      <c r="DH2" s="4"/>
-      <c r="DI2" s="4"/>
-      <c r="DJ2" s="4"/>
-      <c r="DK2" s="4"/>
-      <c r="DL2" s="4"/>
-      <c r="DM2" s="4"/>
-      <c r="DN2" s="4"/>
-      <c r="DO2" s="4"/>
-      <c r="DP2" s="4"/>
-      <c r="DQ2" s="4"/>
-      <c r="DR2" s="4"/>
-      <c r="DS2" s="4"/>
-      <c r="DT2" s="4"/>
-      <c r="DU2" s="4"/>
-      <c r="DV2" s="4"/>
-      <c r="DW2" s="4"/>
-      <c r="DX2" s="4"/>
-      <c r="DY2" s="4"/>
-      <c r="DZ2" s="4"/>
-      <c r="EA2" s="4"/>
-      <c r="EB2" s="4"/>
-      <c r="EC2" s="4"/>
-      <c r="ED2" s="4"/>
-      <c r="EE2" s="4"/>
-      <c r="EF2" s="4"/>
-      <c r="EG2" s="4"/>
-      <c r="EH2" s="4"/>
-      <c r="EI2" s="4"/>
-      <c r="EJ2" s="4"/>
-      <c r="EK2" s="4"/>
-      <c r="EL2" s="4"/>
-      <c r="EM2" s="4"/>
-      <c r="EN2" s="4"/>
-      <c r="EO2" s="4"/>
-      <c r="EP2" s="4"/>
-      <c r="EQ2" s="4"/>
-      <c r="ER2" s="4"/>
-      <c r="ES2" s="4"/>
-      <c r="ET2" s="4"/>
-      <c r="EU2" s="4"/>
-      <c r="EV2" s="4"/>
-      <c r="EW2" s="4"/>
-      <c r="EX2" s="4"/>
-      <c r="EY2" s="4"/>
-      <c r="EZ2" s="4"/>
-      <c r="FA2" s="4"/>
-      <c r="FB2" s="4"/>
-      <c r="FC2" s="4"/>
-      <c r="FD2" s="4"/>
-      <c r="FE2" s="4"/>
-      <c r="FF2" s="4"/>
-      <c r="FG2" s="4"/>
-      <c r="FH2" s="4"/>
-      <c r="FI2" s="4"/>
-      <c r="FJ2" s="4"/>
-      <c r="FK2" s="4"/>
-      <c r="FL2" s="4"/>
-      <c r="FM2" s="4"/>
-      <c r="FN2" s="4"/>
-      <c r="FO2" s="4"/>
-      <c r="FP2" s="4"/>
-      <c r="FQ2" s="4"/>
-      <c r="FR2" s="4"/>
-      <c r="FS2" s="4"/>
-      <c r="FT2" s="4"/>
-      <c r="FU2" s="4"/>
-      <c r="FV2" s="4"/>
-      <c r="FW2" s="4"/>
+    <row r="2" customFormat="1" ht="34" customHeight="1" spans="1:203">
+      <c r="A2" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="5"/>
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="5"/>
+      <c r="AJ2" s="5"/>
+      <c r="AK2" s="5"/>
+      <c r="AL2" s="5"/>
+      <c r="AM2" s="5"/>
+      <c r="AN2" s="5"/>
+      <c r="AO2" s="5"/>
+      <c r="AP2" s="5"/>
+      <c r="AQ2" s="5"/>
+      <c r="AR2" s="5"/>
+      <c r="AS2" s="5"/>
+      <c r="AT2" s="5"/>
+      <c r="AU2" s="5"/>
+      <c r="AV2" s="5"/>
+      <c r="AW2" s="5"/>
+      <c r="AX2" s="5"/>
+      <c r="AY2" s="5"/>
+      <c r="AZ2" s="5"/>
+      <c r="BA2" s="5"/>
+      <c r="BB2" s="5"/>
+      <c r="BC2" s="5"/>
+      <c r="BD2" s="5"/>
+      <c r="BE2" s="5"/>
+      <c r="BF2" s="5"/>
+      <c r="BG2" s="5"/>
+      <c r="BH2" s="5"/>
+      <c r="BI2" s="5"/>
+      <c r="BJ2" s="5"/>
+      <c r="BK2" s="5"/>
+      <c r="BL2" s="5"/>
+      <c r="BM2" s="5"/>
+      <c r="BN2" s="5"/>
+      <c r="BO2" s="5"/>
+      <c r="BP2" s="5"/>
+      <c r="BQ2" s="5"/>
+      <c r="BR2" s="5"/>
+      <c r="BS2" s="5"/>
+      <c r="BT2" s="5"/>
+      <c r="BU2" s="5"/>
+      <c r="BV2" s="5"/>
+      <c r="BW2" s="5"/>
+      <c r="BX2" s="5"/>
+      <c r="BY2" s="5"/>
+      <c r="BZ2" s="5"/>
+      <c r="CA2" s="5"/>
+      <c r="CB2" s="5"/>
+      <c r="CC2" s="5"/>
+      <c r="CD2" s="5"/>
+      <c r="CE2" s="5"/>
+      <c r="CF2" s="5"/>
+      <c r="CG2" s="5"/>
+      <c r="CH2" s="5"/>
+      <c r="CI2" s="5"/>
+      <c r="CJ2" s="5"/>
+      <c r="CK2" s="5"/>
+      <c r="CL2" s="5"/>
+      <c r="CM2" s="5"/>
+      <c r="CN2" s="5"/>
+      <c r="CO2" s="5"/>
+      <c r="CP2" s="5"/>
+      <c r="CQ2" s="5"/>
+      <c r="CR2" s="5"/>
+      <c r="CS2" s="5"/>
+      <c r="CT2" s="5"/>
+      <c r="CU2" s="5"/>
+      <c r="CV2" s="5"/>
+      <c r="CW2" s="5"/>
+      <c r="CX2" s="5"/>
+      <c r="CY2" s="5"/>
+      <c r="CZ2" s="5"/>
+      <c r="DA2" s="5"/>
+      <c r="DB2" s="5"/>
+      <c r="DC2" s="5"/>
+      <c r="DD2" s="5"/>
+      <c r="DE2" s="5"/>
+      <c r="DF2" s="5"/>
+      <c r="DG2" s="5"/>
+      <c r="DH2" s="5"/>
+      <c r="DI2" s="5"/>
+      <c r="DJ2" s="5"/>
+      <c r="DK2" s="5"/>
+      <c r="DL2" s="5"/>
+      <c r="DM2" s="5"/>
+      <c r="DN2" s="5"/>
+      <c r="DO2" s="5"/>
+      <c r="DP2" s="5"/>
+      <c r="DQ2" s="5"/>
+      <c r="DR2" s="5"/>
+      <c r="DS2" s="5"/>
+      <c r="DT2" s="5"/>
+      <c r="DU2" s="5"/>
+      <c r="DV2" s="5"/>
+      <c r="DW2" s="5"/>
+      <c r="DX2" s="5"/>
+      <c r="DY2" s="5"/>
+      <c r="DZ2" s="5"/>
+      <c r="EA2" s="5"/>
+      <c r="EB2" s="5"/>
+      <c r="EC2" s="5"/>
+      <c r="ED2" s="5"/>
+      <c r="EE2" s="5"/>
+      <c r="EF2" s="5"/>
+      <c r="EG2" s="5"/>
+      <c r="EH2" s="5"/>
+      <c r="EI2" s="5"/>
+      <c r="EJ2" s="5"/>
+      <c r="EK2" s="5"/>
+      <c r="EL2" s="5"/>
+      <c r="EM2" s="5"/>
+      <c r="EN2" s="5"/>
+      <c r="EO2" s="5"/>
+      <c r="EP2" s="5"/>
+      <c r="EQ2" s="5"/>
+      <c r="ER2" s="5"/>
+      <c r="ES2" s="5"/>
+      <c r="ET2" s="5"/>
+      <c r="EU2" s="5"/>
+      <c r="EV2" s="5"/>
+      <c r="EW2" s="5"/>
+      <c r="EX2" s="5"/>
+      <c r="EY2" s="5"/>
+      <c r="EZ2" s="5"/>
+      <c r="FA2" s="5"/>
+      <c r="FB2" s="5"/>
+      <c r="FC2" s="5"/>
+      <c r="FD2" s="5"/>
+      <c r="FE2" s="5"/>
+      <c r="FF2" s="5"/>
+      <c r="FG2" s="5"/>
+      <c r="FH2" s="5"/>
+      <c r="FI2" s="5"/>
+      <c r="FJ2" s="5"/>
+      <c r="FK2" s="5"/>
+      <c r="FL2" s="5"/>
+      <c r="FM2" s="5"/>
+      <c r="FN2" s="5"/>
+      <c r="FO2" s="5"/>
+      <c r="FP2" s="5"/>
+      <c r="FQ2" s="5"/>
+      <c r="FR2" s="5"/>
+      <c r="FS2" s="5"/>
+      <c r="FT2" s="5"/>
+      <c r="FU2" s="5"/>
+      <c r="FV2" s="5"/>
+      <c r="FW2" s="5"/>
+      <c r="FX2" s="5"/>
+      <c r="FY2" s="5"/>
+      <c r="FZ2" s="5"/>
+      <c r="GA2" s="5"/>
+      <c r="GB2" s="5"/>
+      <c r="GC2" s="5"/>
+      <c r="GD2" s="5"/>
+      <c r="GE2" s="5"/>
+      <c r="GF2" s="5"/>
+      <c r="GG2" s="5"/>
+      <c r="GH2" s="5"/>
+      <c r="GI2" s="5"/>
+      <c r="GJ2" s="5"/>
+      <c r="GK2" s="5"/>
+      <c r="GL2" s="5"/>
+      <c r="GM2" s="5"/>
+      <c r="GN2" s="5"/>
+      <c r="GO2" s="5"/>
+      <c r="GP2" s="5"/>
+      <c r="GQ2" s="5"/>
+      <c r="GR2" s="5"/>
+      <c r="GS2" s="5"/>
+      <c r="GT2" s="5"/>
+      <c r="GU2" s="5"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="46" customHeight="1" spans="1:179">
+    <row r="3" s="1" customFormat="1" ht="46" customHeight="1" spans="1:203">
       <c r="A3" s="1" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>185</v>
+        <v>208</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>209</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J3" s="1"/>
+        <v>212</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>213</v>
+      </c>
       <c r="K3" s="1" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>193</v>
+        <v>217</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>196</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="T3" s="1"/>
       <c r="U3" s="1" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>200</v>
+        <v>224</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AD3" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="AG3" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="AP3" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="AQ3" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="AR3" s="6"/>
+      <c r="AS3" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="AT3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="AU3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="AV3" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="AW3" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="AX3" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="AY3" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="AZ3" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="BA3" s="1"/>
+      <c r="BB3" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="BC3" s="1"/>
+      <c r="BD3" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="BE3" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="BF3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="BG3" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="BH3" s="1"/>
+      <c r="BI3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="BJ3" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="BK3" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="BL3" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="BM3" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="BN3" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="BO3" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="BP3" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="BQ3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="BR3" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="BS3" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="BT3" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="BU3" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="BV3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="BW3" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="BX3" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="BY3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="BZ3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CA3" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="CB3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CC3" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="CD3" s="1">
+        <v>2.824</v>
+      </c>
+      <c r="CE3" s="1">
+        <v>1.594</v>
+      </c>
+      <c r="CF3" s="1">
+        <v>1.114</v>
+      </c>
+      <c r="CG3" s="1">
+        <v>0.851</v>
+      </c>
+      <c r="CH3" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="CI3" s="1">
+        <v>0.638</v>
+      </c>
+      <c r="CJ3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CK3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CL3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CM3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CN3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CO3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CP3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CQ3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CR3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CS3" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="CT3" s="6"/>
+      <c r="CU3" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="CV3" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="CW3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CX3" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="CY3" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="CZ3" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="DA3" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="DB3" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="DC3" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="DD3" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="DE3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="DF3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="DG3" s="10"/>
+      <c r="DH3" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="DI3" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="DJ3" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="DK3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="DL3" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="DM3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="DN3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="DO3" s="1"/>
+      <c r="DP3" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="DQ3" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="DR3" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="DS3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="DT3" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="DU3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="DV3" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="DW3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="DX3" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="DY3" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="DZ3" s="1">
+        <v>166.43</v>
+      </c>
+      <c r="EA3" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="EB3" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="EC3" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="ED3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EE3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EF3" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="EG3" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="EH3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EJ3" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="EK3" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="EL3" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="EM3" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="EN3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EP3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EQ3" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="ER3" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="ES3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="ET3" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="EU3" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="EV3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EW3" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="EX3" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="EY3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EZ3" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="FA3" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="FB3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="FC3" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="FD3" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="FE3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="FG3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="FH3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="FI3" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="FJ3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="FK3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="FL3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="FN3" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="FO3" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="FP3" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="FQ3" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="FR3" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="FS3" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="FT3" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="FU3" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="FV3" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="FW3" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="FX3" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="FY3" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="GB3" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="GC3" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="GD3" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="GE3" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="GF3" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="GG3" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="GH3" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="GI3" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="GJ3" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="GK3" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="GL3" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="GM3" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="GN3" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="GO3" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="GP3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="GQ3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="GR3" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="GS3" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="GT3" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="GU3" s="12" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="41" customHeight="1" spans="1:203">
+      <c r="A4" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="AE3" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF3" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="AG3" s="1" t="s">
+      <c r="D4" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="AH3" s="5" t="s">
+      <c r="G4" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="AI3" s="5"/>
-      <c r="AJ3" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="AK3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AL3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AM3" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="AN3" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="AO3" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="AG4" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="AI4" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="AK4" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="AL4" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="AM4" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="AN4" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="AO4" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="AP4" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="AQ4" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="AR4" s="6"/>
+      <c r="AS4" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="AT4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="AU4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="AV4" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="AW4" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="AX4" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="AY4" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="AZ4" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="BA4" s="1"/>
+      <c r="BB4" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="BC4" s="1"/>
+      <c r="BD4" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="BE4" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="BF4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="BG4" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="BH4" s="1"/>
+      <c r="BI4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="BJ4" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="BK4" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="BL4" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="BM4" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="BN4" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="BO4" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="BP4" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="AP3" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="AQ3" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="AR3" s="1"/>
-      <c r="AS3" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="AT3" s="1"/>
-      <c r="AU3" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="AV3" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="AW3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AX3" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="AY3" s="1"/>
-      <c r="AZ3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="BA3" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="BB3" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="BC3" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="BD3" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="BE3" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="BF3" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="BG3" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="BH3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="BI3" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="BJ3" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="BK3" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="BL3" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="BM3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="BN3" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="BO3" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="BP3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="BQ3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="BR3" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="BS3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="BT3" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="BU3" s="1">
-        <v>2.824</v>
-      </c>
-      <c r="BV3" s="1">
-        <v>1.594</v>
-      </c>
-      <c r="BW3" s="1">
-        <v>1.114</v>
-      </c>
-      <c r="BX3" s="1">
-        <v>0.851</v>
-      </c>
-      <c r="BY3" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="BZ3" s="1">
-        <v>0.638</v>
-      </c>
-      <c r="CA3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CB3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CC3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CD3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CE3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CF3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CG3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CH3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CI3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CJ3" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="CK3" s="5"/>
-      <c r="CL3" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="CM3" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="CN3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CO3" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="CP3" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="CQ3" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="CR3" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="CS3" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="CT3" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="CU3" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="CV3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CW3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CX3" s="9"/>
-      <c r="CY3" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="CZ3" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="DA3" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="DB3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="DC3" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="DD3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="DE3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="DF3" s="1"/>
-      <c r="DG3" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="DH3" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="DI3" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="DJ3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="DK3" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="DL3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="DM3" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="DN3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="DO3" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="DP3" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="DQ3" s="1">
-        <v>166.43</v>
-      </c>
-      <c r="DR3" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="DS3" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="DT3" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="DU3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="DV3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="DW3" s="1" t="s">
+      <c r="BQ4" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="BR4" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="BS4" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="BT4" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="BU4" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="BV4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="BW4" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="BX4" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="BY4" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="BZ4" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="CA4" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="CB4" s="1"/>
+      <c r="CC4" s="1"/>
+      <c r="CD4" s="1"/>
+      <c r="CE4" s="1"/>
+      <c r="CF4" s="1"/>
+      <c r="CG4" s="1"/>
+      <c r="CH4" s="1"/>
+      <c r="CI4" s="1"/>
+      <c r="CJ4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CK4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CL4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CM4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CN4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CO4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CP4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CQ4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CR4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CS4" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="CT4" s="6"/>
+      <c r="CU4" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="CV4" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="CW4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="CX4" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="CY4" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="CZ4" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="DA4" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="DB4" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="DC4" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="DD4" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="DE4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="DF4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="DG4" s="10"/>
+      <c r="DH4" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="DI4" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="DJ4" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="DK4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="DL4" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="DM4" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="DN4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="DO4" s="1"/>
+      <c r="DP4" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="DQ4" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="DR4" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="DS4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="DT4" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="DU4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="DV4" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="DX3" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="DY3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="EA3" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="EB3" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="EC3" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="ED3" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="EE3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="EG3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="EI3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="EJ3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="EK3" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="EL3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="EM3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="EN3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="EP3" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="EQ3" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="ER3" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="ES3" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="ET3" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="EU3" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="EV3" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="EW3" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="EX3" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="EY3" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="EZ3" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="FA3" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="FD3" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="FE3" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="FF3" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="FG3" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="FH3" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="FI3" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="FJ3" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="FK3" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="FL3" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="FN3" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="FO3" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="FP3" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="FQ3" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="FR3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="FS3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="FT3" s="1" t="s">
+      <c r="DW4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="DX4" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="FU3" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="FV3" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="FW3" s="11" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="41" customHeight="1" spans="1:179">
-      <c r="A4" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="DY4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="DZ4" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="EA4" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="EB4" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="EC4" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="ED4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EE4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EF4" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="EG4" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="EH4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EJ4" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="EK4" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="N4" s="1" t="s">
+      <c r="EL4" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="EM4" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="EN4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EP4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="EQ4" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="ER4" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="ES4" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="ET4" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="EU4" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="O4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="X4" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="AC4" s="1" t="s">
+      <c r="EV4" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="EW4" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="EX4" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="EY4" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="EZ4" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="FA4" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="FB4" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="FC4" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="FD4" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="FE4" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="FG4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="FH4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="FI4" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="FJ4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="FK4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="FL4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="FN4" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="FO4" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="FP4" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="FQ4" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="FR4" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="FS4" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="FT4" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="FU4" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="FV4" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="FW4" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AD4" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="AE4" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="AF4" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="AG4" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH4" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="AI4" s="5"/>
-      <c r="AJ4" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="AK4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AL4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AM4" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="AN4" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="AO4" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="AP4" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="AQ4" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="AR4" s="1"/>
-      <c r="AS4" s="1" t="s">
+      <c r="FX4" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="FY4" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="AT4" s="1"/>
-      <c r="AU4" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="AV4" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="AW4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AX4" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="AY4" s="1"/>
-      <c r="AZ4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="BA4" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="BB4" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="BC4" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="BD4" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="BE4" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="BF4" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="BG4" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="BH4" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="BI4" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="BJ4" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="BK4" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="BL4" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="BM4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="BN4" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="BO4" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="BP4" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="BQ4" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="BR4" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="BS4" s="1"/>
-      <c r="BT4" s="1"/>
-      <c r="BU4" s="1"/>
-      <c r="BV4" s="1"/>
-      <c r="BW4" s="1"/>
-      <c r="BX4" s="1"/>
-      <c r="BY4" s="1"/>
-      <c r="BZ4" s="1"/>
-      <c r="CA4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CB4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CC4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CD4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CE4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CF4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CG4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CH4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CI4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CJ4" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="CK4" s="5"/>
-      <c r="CL4" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="CM4" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="CN4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CO4" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="CP4" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="CQ4" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="CR4" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="CS4" s="1" t="s">
+      <c r="GB4" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="GC4" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="GD4" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="GE4" s="11" t="s">
+        <v>413</v>
+      </c>
+      <c r="GF4" s="11" t="s">
+        <v>414</v>
+      </c>
+      <c r="GG4" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="GH4" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="GI4" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="GJ4" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="GK4" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="GL4" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="GM4" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="GN4" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="GO4" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="GP4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="GQ4" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="GR4" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="CT4" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="CU4" s="1" t="s">
+      <c r="GS4" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="CV4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CW4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CX4" s="9"/>
-      <c r="CY4" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="CZ4" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="DA4" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="DB4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="DC4" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="DD4" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="DE4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="DF4" s="1"/>
-      <c r="DG4" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="DH4" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="DI4" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="DJ4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="DK4" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="DL4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="DM4" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="DN4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="DO4" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="DP4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="DQ4" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="DR4" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="DS4" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="DT4" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="DU4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="DV4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="DW4" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="DX4" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="DY4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="EA4" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="EB4" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="EC4" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="ED4" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="EE4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="EG4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="EI4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="EJ4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="EK4" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="EL4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="EM4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="EN4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="EP4" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="EQ4" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="ER4" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="ES4" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="ET4" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="EU4" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="EV4" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="EW4" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="EX4" s="10" t="s">
-        <v>351</v>
-      </c>
-      <c r="EY4" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="EZ4" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="FA4" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="FD4" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="FE4" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="FF4" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="FG4" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="FH4" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="FI4" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="FJ4" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="FK4" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="FL4" s="10" t="s">
-        <v>360</v>
-      </c>
-      <c r="FN4" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="FO4" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="FP4" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="FQ4" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="FR4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="FS4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="FT4" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="FU4" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="FV4" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="FW4" s="11" t="s">
-        <v>286</v>
+      <c r="GT4" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="GU4" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:FW2"/>
+    <mergeCell ref="A2:GU2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
